--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -614,8 +614,9 @@
     <row r="106"/>
     <row r="107"/>
     <row r="108"/>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -615,8 +615,9 @@
     <row r="107"/>
     <row r="108"/>
     <row r="109"/>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
+    <row r="110"/>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -616,8 +616,9 @@
     <row r="108"/>
     <row r="109"/>
     <row r="110"/>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
+    <row r="111"/>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -617,8 +617,9 @@
     <row r="109"/>
     <row r="110"/>
     <row r="111"/>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
+    <row r="112"/>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -618,8 +618,9 @@
     <row r="110"/>
     <row r="111"/>
     <row r="112"/>
-    <row r="113">
-      <c r="A113" t="inlineStr"/>
+    <row r="113"/>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -619,8 +619,9 @@
     <row r="111"/>
     <row r="112"/>
     <row r="113"/>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -620,8 +620,9 @@
     <row r="112"/>
     <row r="113"/>
     <row r="114"/>
-    <row r="115">
-      <c r="A115" t="inlineStr"/>
+    <row r="115"/>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -621,8 +621,9 @@
     <row r="113"/>
     <row r="114"/>
     <row r="115"/>
-    <row r="116">
-      <c r="A116" t="inlineStr"/>
+    <row r="116"/>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -622,8 +622,9 @@
     <row r="114"/>
     <row r="115"/>
     <row r="116"/>
-    <row r="117">
-      <c r="A117" t="inlineStr"/>
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -623,8 +623,9 @@
     <row r="115"/>
     <row r="116"/>
     <row r="117"/>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
+    <row r="118"/>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -624,8 +624,9 @@
     <row r="116"/>
     <row r="117"/>
     <row r="118"/>
-    <row r="119">
-      <c r="A119" t="inlineStr"/>
+    <row r="119"/>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -625,8 +625,9 @@
     <row r="117"/>
     <row r="118"/>
     <row r="119"/>
-    <row r="120">
-      <c r="A120" t="inlineStr"/>
+    <row r="120"/>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -626,8 +626,9 @@
     <row r="118"/>
     <row r="119"/>
     <row r="120"/>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
+    <row r="121"/>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -627,8 +627,9 @@
     <row r="119"/>
     <row r="120"/>
     <row r="121"/>
-    <row r="122">
-      <c r="A122" t="inlineStr"/>
+    <row r="122"/>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -628,8 +628,9 @@
     <row r="120"/>
     <row r="121"/>
     <row r="122"/>
-    <row r="123">
-      <c r="A123" t="inlineStr"/>
+    <row r="123"/>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -629,8 +629,9 @@
     <row r="121"/>
     <row r="122"/>
     <row r="123"/>
-    <row r="124">
-      <c r="A124" t="inlineStr"/>
+    <row r="124"/>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -630,8 +630,9 @@
     <row r="122"/>
     <row r="123"/>
     <row r="124"/>
-    <row r="125">
-      <c r="A125" t="inlineStr"/>
+    <row r="125"/>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -631,8 +631,9 @@
     <row r="123"/>
     <row r="124"/>
     <row r="125"/>
-    <row r="126">
-      <c r="A126" t="inlineStr"/>
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -632,8 +632,9 @@
     <row r="124"/>
     <row r="125"/>
     <row r="126"/>
-    <row r="127">
-      <c r="A127" t="inlineStr"/>
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -633,8 +633,9 @@
     <row r="125"/>
     <row r="126"/>
     <row r="127"/>
-    <row r="128">
-      <c r="A128" t="inlineStr"/>
+    <row r="128"/>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -634,8 +634,9 @@
     <row r="126"/>
     <row r="127"/>
     <row r="128"/>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
+    <row r="129"/>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -635,8 +635,9 @@
     <row r="127"/>
     <row r="128"/>
     <row r="129"/>
-    <row r="130">
-      <c r="A130" t="inlineStr"/>
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -636,8 +636,9 @@
     <row r="128"/>
     <row r="129"/>
     <row r="130"/>
-    <row r="131">
-      <c r="A131" t="inlineStr"/>
+    <row r="131"/>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -637,8 +637,9 @@
     <row r="129"/>
     <row r="130"/>
     <row r="131"/>
-    <row r="132">
-      <c r="A132" t="inlineStr"/>
+    <row r="132"/>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -638,8 +638,9 @@
     <row r="130"/>
     <row r="131"/>
     <row r="132"/>
-    <row r="133">
-      <c r="A133" t="inlineStr"/>
+    <row r="133"/>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -639,8 +639,9 @@
     <row r="131"/>
     <row r="132"/>
     <row r="133"/>
-    <row r="134">
-      <c r="A134" t="inlineStr"/>
+    <row r="134"/>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -640,8 +640,9 @@
     <row r="132"/>
     <row r="133"/>
     <row r="134"/>
-    <row r="135">
-      <c r="A135" t="inlineStr"/>
+    <row r="135"/>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -641,8 +641,9 @@
     <row r="133"/>
     <row r="134"/>
     <row r="135"/>
-    <row r="136">
-      <c r="A136" t="inlineStr"/>
+    <row r="136"/>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -642,8 +642,9 @@
     <row r="134"/>
     <row r="135"/>
     <row r="136"/>
-    <row r="137">
-      <c r="A137" t="inlineStr"/>
+    <row r="137"/>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -643,8 +643,9 @@
     <row r="135"/>
     <row r="136"/>
     <row r="137"/>
-    <row r="138">
-      <c r="A138" t="inlineStr"/>
+    <row r="138"/>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -644,8 +644,9 @@
     <row r="136"/>
     <row r="137"/>
     <row r="138"/>
-    <row r="139">
-      <c r="A139" t="inlineStr"/>
+    <row r="139"/>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -645,8 +645,9 @@
     <row r="137"/>
     <row r="138"/>
     <row r="139"/>
-    <row r="140">
-      <c r="A140" t="inlineStr"/>
+    <row r="140"/>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -646,8 +646,9 @@
     <row r="138"/>
     <row r="139"/>
     <row r="140"/>
-    <row r="141">
-      <c r="A141" t="inlineStr"/>
+    <row r="141"/>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -647,8 +647,9 @@
     <row r="139"/>
     <row r="140"/>
     <row r="141"/>
-    <row r="142">
-      <c r="A142" t="inlineStr"/>
+    <row r="142"/>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -648,8 +648,9 @@
     <row r="140"/>
     <row r="141"/>
     <row r="142"/>
-    <row r="143">
-      <c r="A143" t="inlineStr"/>
+    <row r="143"/>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -649,8 +649,9 @@
     <row r="141"/>
     <row r="142"/>
     <row r="143"/>
-    <row r="144">
-      <c r="A144" t="inlineStr"/>
+    <row r="144"/>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -650,8 +650,9 @@
     <row r="142"/>
     <row r="143"/>
     <row r="144"/>
-    <row r="145">
-      <c r="A145" t="inlineStr"/>
+    <row r="145"/>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -651,8 +651,9 @@
     <row r="143"/>
     <row r="144"/>
     <row r="145"/>
-    <row r="146">
-      <c r="A146" t="inlineStr"/>
+    <row r="146"/>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -652,8 +652,9 @@
     <row r="144"/>
     <row r="145"/>
     <row r="146"/>
-    <row r="147">
-      <c r="A147" t="inlineStr"/>
+    <row r="147"/>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -653,8 +653,9 @@
     <row r="145"/>
     <row r="146"/>
     <row r="147"/>
-    <row r="148">
-      <c r="A148" t="inlineStr"/>
+    <row r="148"/>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -654,8 +654,9 @@
     <row r="146"/>
     <row r="147"/>
     <row r="148"/>
-    <row r="149">
-      <c r="A149" t="inlineStr"/>
+    <row r="149"/>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -655,8 +655,9 @@
     <row r="147"/>
     <row r="148"/>
     <row r="149"/>
-    <row r="150">
-      <c r="A150" t="inlineStr"/>
+    <row r="150"/>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -656,8 +656,9 @@
     <row r="148"/>
     <row r="149"/>
     <row r="150"/>
-    <row r="151">
-      <c r="A151" t="inlineStr"/>
+    <row r="151"/>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D152"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -657,8 +657,9 @@
     <row r="149"/>
     <row r="150"/>
     <row r="151"/>
-    <row r="152">
-      <c r="A152" t="inlineStr"/>
+    <row r="152"/>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:D154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -658,8 +658,9 @@
     <row r="150"/>
     <row r="151"/>
     <row r="152"/>
-    <row r="153">
-      <c r="A153" t="inlineStr"/>
+    <row r="153"/>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -659,8 +659,9 @@
     <row r="151"/>
     <row r="152"/>
     <row r="153"/>
-    <row r="154">
-      <c r="A154" t="inlineStr"/>
+    <row r="154"/>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -660,8 +660,9 @@
     <row r="152"/>
     <row r="153"/>
     <row r="154"/>
-    <row r="155">
-      <c r="A155" t="inlineStr"/>
+    <row r="155"/>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D156"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -661,8 +661,9 @@
     <row r="153"/>
     <row r="154"/>
     <row r="155"/>
-    <row r="156">
-      <c r="A156" t="inlineStr"/>
+    <row r="156"/>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -662,8 +662,9 @@
     <row r="154"/>
     <row r="155"/>
     <row r="156"/>
-    <row r="157">
-      <c r="A157" t="inlineStr"/>
+    <row r="157"/>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/puzzles_database.xlsx
+++ b/data/puzzles_database.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -663,8 +663,9 @@
     <row r="155"/>
     <row r="156"/>
     <row r="157"/>
-    <row r="158">
-      <c r="A158" t="inlineStr"/>
+    <row r="158"/>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
